--- a/docs/HeatShield_Agri_Budget.xlsx
+++ b/docs/HeatShield_Agri_Budget.xlsx
@@ -502,7 +502,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Activate AI: Economic Opportunity Challenge</t>
+          <t>Wayesu Community Research Organisation Ltd | Activate AI: Economic Opportunity Challenge</t>
         </is>
       </c>
     </row>
